--- a/Madison_Inspire_2026/LAP_consumption.xlsx
+++ b/Madison_Inspire_2026/LAP_consumption.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daswyga\Documents\GitHub\mri_analysis\Madison_Inspire_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B44A5E82-8805-4879-959C-D35549B19B26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F89C4B46-C593-4503-B4B9-69CDB10CEE87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="835" activeTab="1" xr2:uid="{4BEB7E78-824E-4BFE-AAEC-F3A37821A838}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="835" activeTab="6" xr2:uid="{4BEB7E78-824E-4BFE-AAEC-F3A37821A838}"/>
   </bookViews>
   <sheets>
     <sheet name="suspicious_values" sheetId="19" r:id="rId1"/>
@@ -25,6 +25,9 @@
     <sheet name="W_g" sheetId="15" r:id="rId10"/>
     <sheet name="W_per_kg" sheetId="18" r:id="rId11"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId12"/>
+  </externalReferences>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -631,6 +634,48 @@
 </styleSheet>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="suspicious_values"/>
+      <sheetName val="notes"/>
+      <sheetName val="rat_weight"/>
+      <sheetName val="eth_ON"/>
+      <sheetName val="eth_OFF"/>
+      <sheetName val="E_g"/>
+      <sheetName val="E_per_kg"/>
+      <sheetName val="water_ON"/>
+      <sheetName val="water_OFF"/>
+      <sheetName val="W_g"/>
+      <sheetName val="W_per_kg"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6">
+        <row r="10">
+          <cell r="G10">
+            <v>0.29730434782608955</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -50787,8 +50832,8 @@
         <v>0.53348754448398727</v>
       </c>
       <c r="H9" s="39">
-        <f>E_g!H9/(rat_weight!H9/1000)*0.1578</f>
-        <v>1.0529359430605061</v>
+        <f>E_g!H9/(rat_weight!H9/1000)*[1]E_per_kg!$G$10</f>
+        <v>1.983792356490826</v>
       </c>
       <c r="I9" s="39">
         <f>E_g!I9/(rat_weight!I9/1000)*0.1578</f>
